--- a/output/yearly_total_coral_cover_iteration_99_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_99_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.264772250185204</v>
+        <v>1.292221915995945</v>
       </c>
       <c r="C3" t="n">
-        <v>4.61251273224871</v>
+        <v>4.643526142225867</v>
       </c>
       <c r="D3" t="n">
-        <v>6.034513616367031</v>
+        <v>6.045597547947978</v>
       </c>
       <c r="E3" t="n">
-        <v>11.91179859880095</v>
+        <v>11.98134560616979</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.408555719830252</v>
+        <v>1.472406451896941</v>
       </c>
       <c r="C4" t="n">
-        <v>5.082143674238289</v>
+        <v>5.151480825779942</v>
       </c>
       <c r="D4" t="n">
-        <v>6.276280510960856</v>
+        <v>6.307901197915285</v>
       </c>
       <c r="E4" t="n">
-        <v>12.7669799050294</v>
+        <v>12.93178847559217</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.603609392848991</v>
+        <v>1.706048947055462</v>
       </c>
       <c r="C5" t="n">
-        <v>5.690486141075615</v>
+        <v>5.782538513080241</v>
       </c>
       <c r="D5" t="n">
-        <v>6.631773041432002</v>
+        <v>6.610695243353632</v>
       </c>
       <c r="E5" t="n">
-        <v>13.92586857535661</v>
+        <v>14.09928270348933</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.824916407373429</v>
+        <v>1.957909589503562</v>
       </c>
       <c r="C6" t="n">
-        <v>6.418595794944079</v>
+        <v>6.504975879768734</v>
       </c>
       <c r="D6" t="n">
-        <v>6.985293346792122</v>
+        <v>7.003714572380703</v>
       </c>
       <c r="E6" t="n">
-        <v>15.22880554910963</v>
+        <v>15.466600041653</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.072744532262921</v>
+        <v>2.244698281507642</v>
       </c>
       <c r="C7" t="n">
-        <v>7.258461582323919</v>
+        <v>7.312321156595468</v>
       </c>
       <c r="D7" t="n">
-        <v>7.352236653412038</v>
+        <v>7.469192458975176</v>
       </c>
       <c r="E7" t="n">
-        <v>16.68344276799888</v>
+        <v>17.02621189707829</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.288973112861808</v>
+        <v>1.419741570617716</v>
       </c>
       <c r="C8" t="n">
-        <v>4.906511471207287</v>
+        <v>4.808588800969141</v>
       </c>
       <c r="D8" t="n">
-        <v>5.546749772067449</v>
+        <v>5.755879343119739</v>
       </c>
       <c r="E8" t="n">
-        <v>11.74223435613655</v>
+        <v>11.9842097147066</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.617877225332774</v>
+        <v>1.795284054547484</v>
       </c>
       <c r="C9" t="n">
-        <v>5.988176918797567</v>
+        <v>5.715861498743346</v>
       </c>
       <c r="D9" t="n">
-        <v>6.062113330133844</v>
+        <v>6.410126258613332</v>
       </c>
       <c r="E9" t="n">
-        <v>13.66816747426418</v>
+        <v>13.92127181190416</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.965615795365264</v>
+        <v>2.19401000356494</v>
       </c>
       <c r="C10" t="n">
-        <v>7.282363028671528</v>
+        <v>6.744525913405117</v>
       </c>
       <c r="D10" t="n">
-        <v>6.539941596101724</v>
+        <v>7.002912117120601</v>
       </c>
       <c r="E10" t="n">
-        <v>15.78792042013852</v>
+        <v>15.94144803409066</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.307982533675723</v>
+        <v>2.60682167678651</v>
       </c>
       <c r="C11" t="n">
-        <v>8.694891129162224</v>
+        <v>7.897546115095058</v>
       </c>
       <c r="D11" t="n">
-        <v>7.044592666263679</v>
+        <v>7.63090573579252</v>
       </c>
       <c r="E11" t="n">
-        <v>18.04746632910162</v>
+        <v>18.13527352767409</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.65580578366994</v>
+        <v>3.026784312926981</v>
       </c>
       <c r="C12" t="n">
-        <v>10.21998912689583</v>
+        <v>9.14507558566403</v>
       </c>
       <c r="D12" t="n">
-        <v>7.564691949333517</v>
+        <v>8.252721490333263</v>
       </c>
       <c r="E12" t="n">
-        <v>20.44048685989928</v>
+        <v>20.42458138892427</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.01177667947956</v>
+        <v>3.441639523938778</v>
       </c>
       <c r="C13" t="n">
-        <v>11.78255175638287</v>
+        <v>10.4481567182035</v>
       </c>
       <c r="D13" t="n">
-        <v>8.003783556242306</v>
+        <v>8.805142046609047</v>
       </c>
       <c r="E13" t="n">
-        <v>22.79811199210474</v>
+        <v>22.69493828875132</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.752282207401962</v>
+        <v>1.992240981273967</v>
       </c>
       <c r="C14" t="n">
-        <v>8.278577698584186</v>
+        <v>7.500110673978719</v>
       </c>
       <c r="D14" t="n">
-        <v>6.091852497098925</v>
+        <v>6.720681536623092</v>
       </c>
       <c r="E14" t="n">
-        <v>16.12271240308507</v>
+        <v>16.21303319187578</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.804010493938727</v>
+        <v>2.058636578512179</v>
       </c>
       <c r="C15" t="n">
-        <v>8.968334000633909</v>
+        <v>7.985103857353686</v>
       </c>
       <c r="D15" t="n">
-        <v>6.091449980540184</v>
+        <v>6.811139770092395</v>
       </c>
       <c r="E15" t="n">
-        <v>16.86379447511282</v>
+        <v>16.85488020595826</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.102648328093564</v>
+        <v>2.414097969788822</v>
       </c>
       <c r="C16" t="n">
-        <v>10.66540271714903</v>
+        <v>9.427683933973949</v>
       </c>
       <c r="D16" t="n">
-        <v>6.579368772073807</v>
+        <v>7.360083998921998</v>
       </c>
       <c r="E16" t="n">
-        <v>19.3474198173164</v>
+        <v>19.20186590268477</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.687427954059418</v>
+        <v>1.95163589622632</v>
       </c>
       <c r="C17" t="n">
-        <v>9.912902919320894</v>
+        <v>8.702702524295852</v>
       </c>
       <c r="D17" t="n">
-        <v>6.107099038945877</v>
+        <v>6.904287992271331</v>
       </c>
       <c r="E17" t="n">
-        <v>17.70742991232619</v>
+        <v>17.5586264127935</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.935005090116378</v>
+        <v>2.250303182812284</v>
       </c>
       <c r="C18" t="n">
-        <v>11.64562871245426</v>
+        <v>10.20463906711488</v>
       </c>
       <c r="D18" t="n">
-        <v>6.553097203508162</v>
+        <v>7.422690050021818</v>
       </c>
       <c r="E18" t="n">
-        <v>20.1337310060788</v>
+        <v>19.87763229994898</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.947915072427224</v>
+        <v>2.281709291871139</v>
       </c>
       <c r="C19" t="n">
-        <v>12.53554373644582</v>
+        <v>10.97159019114953</v>
       </c>
       <c r="D19" t="n">
-        <v>6.663887431932414</v>
+        <v>7.57504747624388</v>
       </c>
       <c r="E19" t="n">
-        <v>21.14734624080546</v>
+        <v>20.82834695926454</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.179735157831023</v>
+        <v>2.567937835044297</v>
       </c>
       <c r="C20" t="n">
-        <v>14.42850057238931</v>
+        <v>12.67311604224193</v>
       </c>
       <c r="D20" t="n">
-        <v>7.069211789107753</v>
+        <v>8.172980915515399</v>
       </c>
       <c r="E20" t="n">
-        <v>23.67744751932809</v>
+        <v>23.41403479280163</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.3043009124771</v>
+        <v>1.541795499611446</v>
       </c>
       <c r="C21" t="n">
-        <v>10.63746217748617</v>
+        <v>9.422578845911868</v>
       </c>
       <c r="D21" t="n">
-        <v>5.888012221266161</v>
+        <v>6.865253703550477</v>
       </c>
       <c r="E21" t="n">
-        <v>17.82977531122943</v>
+        <v>17.82962804907379</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_99_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_99_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.292221915995945</v>
+        <v>1.266028887246641</v>
       </c>
       <c r="C3" t="n">
-        <v>4.643526142225867</v>
+        <v>4.658527247146758</v>
       </c>
       <c r="D3" t="n">
-        <v>6.045597547947978</v>
+        <v>6.044075839006394</v>
       </c>
       <c r="E3" t="n">
-        <v>11.98134560616979</v>
+        <v>11.96863197339979</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.472406451896941</v>
+        <v>1.413120891017786</v>
       </c>
       <c r="C4" t="n">
-        <v>5.151480825779942</v>
+        <v>5.192774745287498</v>
       </c>
       <c r="D4" t="n">
-        <v>6.307901197915285</v>
+        <v>6.271508067340068</v>
       </c>
       <c r="E4" t="n">
-        <v>12.93178847559217</v>
+        <v>12.87740370364535</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.706048947055462</v>
+        <v>1.613689141208509</v>
       </c>
       <c r="C5" t="n">
-        <v>5.782538513080241</v>
+        <v>5.864370071281325</v>
       </c>
       <c r="D5" t="n">
-        <v>6.610695243353632</v>
+        <v>6.567373419406406</v>
       </c>
       <c r="E5" t="n">
-        <v>14.09928270348933</v>
+        <v>14.04543263189624</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.957909589503562</v>
+        <v>1.843187323882159</v>
       </c>
       <c r="C6" t="n">
-        <v>6.504975879768734</v>
+        <v>6.698087267949329</v>
       </c>
       <c r="D6" t="n">
-        <v>7.003714572380703</v>
+        <v>6.920706306344941</v>
       </c>
       <c r="E6" t="n">
-        <v>15.466600041653</v>
+        <v>15.46198089817643</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.244698281507642</v>
+        <v>2.099897959420818</v>
       </c>
       <c r="C7" t="n">
-        <v>7.312321156595468</v>
+        <v>7.706276951072779</v>
       </c>
       <c r="D7" t="n">
-        <v>7.469192458975176</v>
+        <v>7.287409329422492</v>
       </c>
       <c r="E7" t="n">
-        <v>17.02621189707829</v>
+        <v>17.09358423991609</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.419741570617716</v>
+        <v>1.30823033974631</v>
       </c>
       <c r="C8" t="n">
-        <v>4.808588800969141</v>
+        <v>5.371368244322517</v>
       </c>
       <c r="D8" t="n">
-        <v>5.755879343119739</v>
+        <v>5.503861080672071</v>
       </c>
       <c r="E8" t="n">
-        <v>11.9842097147066</v>
+        <v>12.1834596647409</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.795284054547484</v>
+        <v>1.654037316687313</v>
       </c>
       <c r="C9" t="n">
-        <v>5.715861498743346</v>
+        <v>6.625026398721792</v>
       </c>
       <c r="D9" t="n">
-        <v>6.410126258613332</v>
+        <v>6.003087782397244</v>
       </c>
       <c r="E9" t="n">
-        <v>13.92127181190416</v>
+        <v>14.28215149780635</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.19401000356494</v>
+        <v>2.014610638054652</v>
       </c>
       <c r="C10" t="n">
-        <v>6.744525913405117</v>
+        <v>8.027196176818608</v>
       </c>
       <c r="D10" t="n">
-        <v>7.002912117120601</v>
+        <v>6.454211201337324</v>
       </c>
       <c r="E10" t="n">
-        <v>15.94144803409066</v>
+        <v>16.49601801621058</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.60682167678651</v>
+        <v>2.401899664315281</v>
       </c>
       <c r="C11" t="n">
-        <v>7.897546115095058</v>
+        <v>9.547781877151087</v>
       </c>
       <c r="D11" t="n">
-        <v>7.63090573579252</v>
+        <v>7.009174747502176</v>
       </c>
       <c r="E11" t="n">
-        <v>18.13527352767409</v>
+        <v>18.95885628896854</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.026784312926981</v>
+        <v>2.777932044212847</v>
       </c>
       <c r="C12" t="n">
-        <v>9.14507558566403</v>
+        <v>11.12855441170076</v>
       </c>
       <c r="D12" t="n">
-        <v>8.252721490333263</v>
+        <v>7.553518172496704</v>
       </c>
       <c r="E12" t="n">
-        <v>20.42458138892427</v>
+        <v>21.46000462841031</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.441639523938778</v>
+        <v>3.126950309452071</v>
       </c>
       <c r="C13" t="n">
-        <v>10.4481567182035</v>
+        <v>12.71312986358593</v>
       </c>
       <c r="D13" t="n">
-        <v>8.805142046609047</v>
+        <v>8.137857632066813</v>
       </c>
       <c r="E13" t="n">
-        <v>22.69493828875132</v>
+        <v>23.97793780510482</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.992240981273967</v>
+        <v>1.792533863276081</v>
       </c>
       <c r="C14" t="n">
-        <v>7.500110673978719</v>
+        <v>8.896067552124302</v>
       </c>
       <c r="D14" t="n">
-        <v>6.720681536623092</v>
+        <v>6.211763161695631</v>
       </c>
       <c r="E14" t="n">
-        <v>16.21303319187578</v>
+        <v>16.90036457709601</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2.058636578512179</v>
+        <v>1.839481038493164</v>
       </c>
       <c r="C15" t="n">
-        <v>7.985103857353686</v>
+        <v>9.551443049571304</v>
       </c>
       <c r="D15" t="n">
-        <v>6.811139770092395</v>
+        <v>6.274879721601659</v>
       </c>
       <c r="E15" t="n">
-        <v>16.85488020595826</v>
+        <v>17.66580380966613</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.414097969788822</v>
+        <v>2.128046141202429</v>
       </c>
       <c r="C16" t="n">
-        <v>9.427683933973949</v>
+        <v>11.18671074810409</v>
       </c>
       <c r="D16" t="n">
-        <v>7.360083998921998</v>
+        <v>6.787872349501745</v>
       </c>
       <c r="E16" t="n">
-        <v>19.20186590268477</v>
+        <v>20.10262923880826</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.95163589622632</v>
+        <v>1.6997685227018</v>
       </c>
       <c r="C17" t="n">
-        <v>8.702702524295852</v>
+        <v>10.1978944603867</v>
       </c>
       <c r="D17" t="n">
-        <v>6.904287992271331</v>
+        <v>6.339056569028273</v>
       </c>
       <c r="E17" t="n">
-        <v>17.5586264127935</v>
+        <v>18.23671955211677</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.250303182812284</v>
+        <v>1.940915211295944</v>
       </c>
       <c r="C18" t="n">
-        <v>10.20463906711488</v>
+        <v>11.81704186161575</v>
       </c>
       <c r="D18" t="n">
-        <v>7.422690050021818</v>
+        <v>6.777897792826596</v>
       </c>
       <c r="E18" t="n">
-        <v>19.87763229994898</v>
+        <v>20.53585486573829</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.281709291871139</v>
+        <v>1.94921097939683</v>
       </c>
       <c r="C19" t="n">
-        <v>10.97159019114953</v>
+        <v>12.56240435363402</v>
       </c>
       <c r="D19" t="n">
-        <v>7.57504747624388</v>
+        <v>6.89147618473091</v>
       </c>
       <c r="E19" t="n">
-        <v>20.82834695926454</v>
+        <v>21.40309151776176</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.567937835044297</v>
+        <v>2.185890715936651</v>
       </c>
       <c r="C20" t="n">
-        <v>12.67311604224193</v>
+        <v>14.36442189973312</v>
       </c>
       <c r="D20" t="n">
-        <v>8.172980915515399</v>
+        <v>7.343865526847841</v>
       </c>
       <c r="E20" t="n">
-        <v>23.41403479280163</v>
+        <v>23.89417814251761</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.541795499611446</v>
+        <v>1.306126963206999</v>
       </c>
       <c r="C21" t="n">
-        <v>9.422578845911868</v>
+        <v>10.50498514227511</v>
       </c>
       <c r="D21" t="n">
-        <v>6.865253703550477</v>
+        <v>6.161978735613276</v>
       </c>
       <c r="E21" t="n">
-        <v>17.82962804907379</v>
+        <v>17.97309084109538</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_99_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_99_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.266028887246641</v>
+        <v>2.605528476523437</v>
       </c>
       <c r="C3" t="n">
-        <v>4.658527247146758</v>
+        <v>7.84897189003933</v>
       </c>
       <c r="D3" t="n">
-        <v>6.044075839006394</v>
+        <v>8.124931987926983</v>
       </c>
       <c r="E3" t="n">
-        <v>11.96863197339979</v>
+        <v>18.57943235448975</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.413120891017786</v>
+        <v>1.103907635855439</v>
       </c>
       <c r="C4" t="n">
-        <v>5.192774745287498</v>
+        <v>4.814455628536464</v>
       </c>
       <c r="D4" t="n">
-        <v>6.271508067340068</v>
+        <v>5.664143708752904</v>
       </c>
       <c r="E4" t="n">
-        <v>12.87740370364535</v>
+        <v>11.58250697314481</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.613689141208509</v>
+        <v>1.235014362809227</v>
       </c>
       <c r="C5" t="n">
-        <v>5.864370071281325</v>
+        <v>5.79905534587563</v>
       </c>
       <c r="D5" t="n">
-        <v>6.567373419406406</v>
+        <v>5.89376183247519</v>
       </c>
       <c r="E5" t="n">
-        <v>14.04543263189624</v>
+        <v>12.92783154116005</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.843187323882159</v>
+        <v>1.377908126196369</v>
       </c>
       <c r="C6" t="n">
-        <v>6.698087267949329</v>
+        <v>7.039469381134276</v>
       </c>
       <c r="D6" t="n">
-        <v>6.920706306344941</v>
+        <v>6.185039284328506</v>
       </c>
       <c r="E6" t="n">
-        <v>15.46198089817643</v>
+        <v>14.60241679165915</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.099897959420818</v>
+        <v>1.522688864875221</v>
       </c>
       <c r="C7" t="n">
-        <v>7.706276951072779</v>
+        <v>8.505594395194828</v>
       </c>
       <c r="D7" t="n">
-        <v>7.287409329422492</v>
+        <v>6.514301250405587</v>
       </c>
       <c r="E7" t="n">
-        <v>17.09358423991609</v>
+        <v>16.54258451047564</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.30823033974631</v>
+        <v>1.66328920796084</v>
       </c>
       <c r="C8" t="n">
-        <v>5.371368244322517</v>
+        <v>10.14071719141922</v>
       </c>
       <c r="D8" t="n">
-        <v>5.503861080672071</v>
+        <v>6.907147939947163</v>
       </c>
       <c r="E8" t="n">
-        <v>12.1834596647409</v>
+        <v>18.71115433932723</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.654037316687313</v>
+        <v>1.782444776063236</v>
       </c>
       <c r="C9" t="n">
-        <v>6.625026398721792</v>
+        <v>11.8636422001747</v>
       </c>
       <c r="D9" t="n">
-        <v>6.003087782397244</v>
+        <v>7.217681496429337</v>
       </c>
       <c r="E9" t="n">
-        <v>14.28215149780635</v>
+        <v>20.86376847266727</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.014610638054652</v>
+        <v>1.094579967895896</v>
       </c>
       <c r="C10" t="n">
-        <v>8.027196176818608</v>
+        <v>8.42282588876917</v>
       </c>
       <c r="D10" t="n">
-        <v>6.454211201337324</v>
+        <v>5.6793417467285</v>
       </c>
       <c r="E10" t="n">
-        <v>16.49601801621058</v>
+        <v>15.19674760339357</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.401899664315281</v>
+        <v>1.020340206500753</v>
       </c>
       <c r="C11" t="n">
-        <v>9.547781877151087</v>
+        <v>9.218424410813743</v>
       </c>
       <c r="D11" t="n">
-        <v>7.009174747502176</v>
+        <v>5.48267804661378</v>
       </c>
       <c r="E11" t="n">
-        <v>18.95885628896854</v>
+        <v>15.72144266392828</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.777932044212847</v>
+        <v>1.088237877726462</v>
       </c>
       <c r="C12" t="n">
-        <v>11.12855441170076</v>
+        <v>11.00705091822692</v>
       </c>
       <c r="D12" t="n">
-        <v>7.553518172496704</v>
+        <v>5.79815285389645</v>
       </c>
       <c r="E12" t="n">
-        <v>21.46000462841031</v>
+        <v>17.89344164984983</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.126950309452071</v>
+        <v>0.8488190650917923</v>
       </c>
       <c r="C13" t="n">
-        <v>12.71312986358593</v>
+        <v>10.45808705444323</v>
       </c>
       <c r="D13" t="n">
-        <v>8.137857632066813</v>
+        <v>5.221356442697364</v>
       </c>
       <c r="E13" t="n">
-        <v>23.97793780510482</v>
+        <v>16.52826256223239</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.792533863276081</v>
+        <v>0.9058782416626169</v>
       </c>
       <c r="C14" t="n">
-        <v>8.896067552124302</v>
+        <v>12.34082389678551</v>
       </c>
       <c r="D14" t="n">
-        <v>6.211763161695631</v>
+        <v>5.50352055037494</v>
       </c>
       <c r="E14" t="n">
-        <v>16.90036457709601</v>
+        <v>18.75022268882307</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.839481038493164</v>
+        <v>0.865734578035965</v>
       </c>
       <c r="C15" t="n">
-        <v>9.551443049571304</v>
+        <v>13.3884272370332</v>
       </c>
       <c r="D15" t="n">
-        <v>6.274879721601659</v>
+        <v>5.496235982409428</v>
       </c>
       <c r="E15" t="n">
-        <v>17.66580380966613</v>
+        <v>19.75039779747859</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.128046141202429</v>
+        <v>0.9319927305955822</v>
       </c>
       <c r="C16" t="n">
-        <v>11.18671074810409</v>
+        <v>15.57934450121559</v>
       </c>
       <c r="D16" t="n">
-        <v>6.787872349501745</v>
+        <v>5.839494249722282</v>
       </c>
       <c r="E16" t="n">
-        <v>20.10262923880826</v>
+        <v>22.35083148153346</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.6997685227018</v>
+        <v>0.5488264191050943</v>
       </c>
       <c r="C17" t="n">
-        <v>10.1978944603867</v>
+        <v>11.55727141907205</v>
       </c>
       <c r="D17" t="n">
-        <v>6.339056569028273</v>
+        <v>4.823218478717112</v>
       </c>
       <c r="E17" t="n">
-        <v>18.23671955211677</v>
+        <v>16.92931631689425</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.940915211295944</v>
+        <v>0.4226816565864218</v>
       </c>
       <c r="C18" t="n">
-        <v>11.81704186161575</v>
+        <v>10.43188420821689</v>
       </c>
       <c r="D18" t="n">
-        <v>6.777897792826596</v>
+        <v>4.337989675893126</v>
       </c>
       <c r="E18" t="n">
-        <v>20.53585486573829</v>
+        <v>15.19255554069643</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.94921097939683</v>
+        <v>0.4876929895616456</v>
       </c>
       <c r="C19" t="n">
-        <v>12.56240435363402</v>
+        <v>12.9488987898419</v>
       </c>
       <c r="D19" t="n">
-        <v>6.89147618473091</v>
+        <v>4.753376947036994</v>
       </c>
       <c r="E19" t="n">
-        <v>21.40309151776176</v>
+        <v>18.18996872644054</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.185890715936651</v>
+        <v>0.5490227686459439</v>
       </c>
       <c r="C20" t="n">
-        <v>14.36442189973312</v>
+        <v>15.64406130987954</v>
       </c>
       <c r="D20" t="n">
-        <v>7.343865526847841</v>
+        <v>5.193661339960562</v>
       </c>
       <c r="E20" t="n">
-        <v>23.89417814251761</v>
+        <v>21.38674541848605</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.306126963206999</v>
+        <v>0.6010946668791946</v>
       </c>
       <c r="C21" t="n">
-        <v>10.50498514227511</v>
+        <v>18.35875079175465</v>
       </c>
       <c r="D21" t="n">
-        <v>6.161978735613276</v>
+        <v>5.533905641821378</v>
       </c>
       <c r="E21" t="n">
-        <v>17.97309084109538</v>
+        <v>24.49375110045522</v>
       </c>
     </row>
   </sheetData>
